--- a/results/Resultados_TFG_Isidro.xlsx
+++ b/results/Resultados_TFG_Isidro.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Hoja 1 - Resultados" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Hoja 2 - Promedios" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Hoja 2 - Medias y desviaciones" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Hoja 3 - Descripciones" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>Modelo</t>
   </si>
@@ -57,6 +57,24 @@
   </si>
   <si>
     <t>ResNet101 – Fine-Tuning</t>
+  </si>
+  <si>
+    <t>Train Acc (media ± std)</t>
+  </si>
+  <si>
+    <t>Train AUC (media ± std)</t>
+  </si>
+  <si>
+    <t>Val Acc (media ± std)</t>
+  </si>
+  <si>
+    <t>Val AUC (media ± std)</t>
+  </si>
+  <si>
+    <t>Test  Acc (media ± std)</t>
+  </si>
+  <si>
+    <t>Test AUC (media ± std)</t>
   </si>
   <si>
     <t>Test Recall (Pneumonia)</t>
@@ -199,8 +217,12 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -2117,7 +2139,12 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="31.0"/>
-    <col customWidth="1" min="2" max="7" width="20.71"/>
+    <col customWidth="1" min="2" max="2" width="22.14"/>
+    <col customWidth="1" min="3" max="3" width="22.86"/>
+    <col customWidth="1" min="4" max="4" width="21.86"/>
+    <col customWidth="1" min="5" max="5" width="21.71"/>
+    <col customWidth="1" min="6" max="6" width="22.14"/>
+    <col customWidth="1" min="7" max="7" width="23.14"/>
     <col customWidth="1" min="8" max="8" width="23.71"/>
     <col customWidth="1" min="9" max="9" width="26.29"/>
     <col customWidth="1" min="10" max="25" width="8.71"/>
@@ -2128,57 +2155,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10">
-        <f>AVERAGE('Hoja 1 - Resultados'!C2:C6)</f>
-        <v>0.90972</v>
-      </c>
-      <c r="C2" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!D2:D6)</f>
-        <v>0.95376</v>
-      </c>
-      <c r="D2" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!E2:E6)</f>
-        <v>0.93352</v>
-      </c>
-      <c r="E2" s="6">
-        <f>AVERAGE('Hoja 1 - Resultados'!F2:F6)</f>
-        <v>0.9905</v>
-      </c>
-      <c r="F2" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!G2:G6)</f>
-        <v>0.83078</v>
-      </c>
-      <c r="G2" s="6">
-        <f>AVERAGE('Hoja 1 - Resultados'!H2:H6)</f>
-        <v>0.9402</v>
+      <c r="B2" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!C2:C6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!C2:C6),4)</f>
+        <v>0.9097 ± 0.0415</v>
+      </c>
+      <c r="C2" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!D2:D6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!D2:D6),4)</f>
+        <v>0.9538 ± 0.0348</v>
+      </c>
+      <c r="D2" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!E2:E6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!E2:E6),4)</f>
+        <v>0.9335 ± 0.0183</v>
+      </c>
+      <c r="E2" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!F2:F6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!F2:F6),4)</f>
+        <v>0.9905 ± 0.0027</v>
+      </c>
+      <c r="F2" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!G2:G6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!G2:G6),4)</f>
+        <v>0.8308 ± 0.092</v>
+      </c>
+      <c r="G2" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!H2:H6),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!H2:H6),4)</f>
+        <v>0.9402 ± 0.0099</v>
       </c>
       <c r="H2" s="8">
         <v>0.97</v>
@@ -2187,36 +2214,36 @@
         <v>0.84</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!C8:C12)</f>
-        <v>0.92684</v>
-      </c>
-      <c r="C3" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!D8:D12)</f>
-        <v>0.97422</v>
-      </c>
-      <c r="D3" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!E8:E12)</f>
-        <v>0.94192</v>
-      </c>
-      <c r="E3" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!F8:F12)</f>
-        <v>0.98858</v>
-      </c>
-      <c r="F3" s="6">
-        <f>AVERAGE('Hoja 1 - Resultados'!G8:G12)</f>
-        <v>0.8894</v>
-      </c>
-      <c r="G3" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!H8:H12)</f>
-        <v>0.9534</v>
+      <c r="B3" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!C8:C12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!C8:C12),4)</f>
+        <v>0.9268 ± 0.0037</v>
+      </c>
+      <c r="C3" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!D8:D12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!D8:D12),4)</f>
+        <v>0.9742 ± 0.002</v>
+      </c>
+      <c r="D3" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!E8:E12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!E8:E12),4)</f>
+        <v>0.9419 ± 0.0124</v>
+      </c>
+      <c r="E3" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!F8:F12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!F8:F12),4)</f>
+        <v>0.9886 ± 0.0025</v>
+      </c>
+      <c r="F3" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!G8:G12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!G8:G12),4)</f>
+        <v>0.8894 ± 0.0073</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!H8:H12),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!H8:H12),4)</f>
+        <v>0.9534 ± 0.0044</v>
       </c>
       <c r="H3" s="8">
         <v>0.96</v>
@@ -2225,36 +2252,36 @@
         <v>0.89</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!C14:C18)</f>
-        <v>0.97398</v>
-      </c>
-      <c r="C4" s="6">
-        <f>AVERAGE('Hoja 1 - Resultados'!D14:D18)</f>
-        <v>0.9941</v>
-      </c>
-      <c r="D4" s="6">
-        <f>AVERAGE('Hoja 1 - Resultados'!E14:E18)</f>
-        <v>0.9662</v>
-      </c>
-      <c r="E4" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!F14:F18)</f>
-        <v>0.99656</v>
-      </c>
-      <c r="F4" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!G14:G18)</f>
-        <v>0.89936</v>
-      </c>
-      <c r="G4" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!H14:H18)</f>
-        <v>0.96934</v>
+      <c r="B4" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!C14:C18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!C14:C18),4)</f>
+        <v>0.974 ± 0.0036</v>
+      </c>
+      <c r="C4" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!D14:D18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!D14:D18),4)</f>
+        <v>0.9941 ± 0.0026</v>
+      </c>
+      <c r="D4" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!E14:E18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!E14:E18),4)</f>
+        <v>0.9662 ± 0.0064</v>
+      </c>
+      <c r="E4" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!F14:F18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!F14:F18),4)</f>
+        <v>0.9966 ± 0.0008</v>
+      </c>
+      <c r="F4" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!G14:G18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!G14:G18),4)</f>
+        <v>0.8994 ± 0.0105</v>
+      </c>
+      <c r="G4" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!H14:H18),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!H14:H18),4)</f>
+        <v>0.9693 ± 0.0031</v>
       </c>
       <c r="H4" s="8">
         <v>0.99</v>
@@ -2263,36 +2290,36 @@
         <v>0.88</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!C20:C24)</f>
-        <v>0.92214</v>
-      </c>
-      <c r="C5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!D20:D24)</f>
-        <v>0.96962</v>
-      </c>
-      <c r="D5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!E20:E24)</f>
-        <v>0.92858</v>
-      </c>
-      <c r="E5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!F20:F24)</f>
-        <v>0.98318</v>
-      </c>
-      <c r="F5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!G20:G24)</f>
-        <v>0.84068</v>
-      </c>
-      <c r="G5" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!H20:H24)</f>
-        <v>0.93112</v>
+      <c r="B5" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!C20:C24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!C20:C24),4)</f>
+        <v>0.9221 ± 0.0078</v>
+      </c>
+      <c r="C5" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!D20:D24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!D20:D24),4)</f>
+        <v>0.9696 ± 0.0025</v>
+      </c>
+      <c r="D5" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!E20:E24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!E20:E24),4)</f>
+        <v>0.9286 ± 0.0105</v>
+      </c>
+      <c r="E5" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!F20:F24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!F20:F24),4)</f>
+        <v>0.9832 ± 0.0035</v>
+      </c>
+      <c r="F5" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!G20:G24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!G20:G24),4)</f>
+        <v>0.8407 ± 0.0091</v>
+      </c>
+      <c r="G5" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!H20:H24),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!H20:H24),4)</f>
+        <v>0.9311 ± 0.0059</v>
       </c>
       <c r="H5" s="8">
         <v>0.96</v>
@@ -2301,36 +2328,36 @@
         <v>0.84</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!C26:C30)</f>
-        <v>0.92986</v>
-      </c>
-      <c r="C6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!D26:D30)</f>
-        <v>0.97374</v>
-      </c>
-      <c r="D6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!E26:E30)</f>
-        <v>0.93086</v>
-      </c>
-      <c r="E6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!F26:F30)</f>
-        <v>0.99066</v>
-      </c>
-      <c r="F6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!G26:G30)</f>
-        <v>0.85354</v>
-      </c>
-      <c r="G6" s="11">
-        <f>AVERAGE('Hoja 1 - Resultados'!H26:H30)</f>
-        <v>0.94386</v>
+      <c r="B6" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!C26:C30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!C26:C30),4)</f>
+        <v>0.9299 ± 0.005</v>
+      </c>
+      <c r="C6" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!D26:D30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!D26:D30),4)</f>
+        <v>0.9737 ± 0.0022</v>
+      </c>
+      <c r="D6" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!E26:E30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!E26:E30),4)</f>
+        <v>0.9309 ± 0.0331</v>
+      </c>
+      <c r="E6" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!F26:F30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!F26:F30),4)</f>
+        <v>0.9907 ± 0.0028</v>
+      </c>
+      <c r="F6" s="11" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!G26:G30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!G26:G30),4)</f>
+        <v>0.8535 ± 0.0421</v>
+      </c>
+      <c r="G6" s="10" t="str">
+        <f>ROUND(AVERAGE('Hoja 1 - Resultados'!H26:H30),4)&amp;" ± "&amp;ROUND(_xlfn.STDEV.S('Hoja 1 - Resultados'!H26:H30),4)</f>
+        <v>0.9439 ± 0.0115</v>
       </c>
       <c r="H6" s="13">
         <v>0.9</v>
@@ -2339,7 +2366,7 @@
         <v>0.91</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3347,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -3355,7 +3382,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -3363,7 +3390,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -3371,7 +3398,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -3379,7 +3406,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -3387,7 +3414,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
